--- a/Logs/Customers.XLSX
+++ b/Logs/Customers.XLSX
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18150" windowHeight="10215"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13740" windowHeight="10215"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,18 +24,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>CustomerID</t>
   </si>
   <si>
-    <t>ContactName</t>
-  </si>
-  <si>
-    <t>ContactTitle</t>
-  </si>
-  <si>
-    <t>CompanyName</t>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
   <si>
     <t>Address</t>
@@ -65,19 +65,25 @@
     <t>John</t>
   </si>
   <si>
-    <t>JD</t>
-  </si>
-  <si>
     <t>Vacant</t>
   </si>
   <si>
+    <t xml:space="preserve">            </t>
+  </si>
+  <si>
     <t xml:space="preserve">C2   </t>
   </si>
   <si>
     <t>Emma</t>
   </si>
   <si>
-    <t>Em</t>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">2222                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">223344556   </t>
   </si>
   <si>
     <t xml:space="preserve">C3   </t>
@@ -86,16 +92,31 @@
     <t>Joe</t>
   </si>
   <si>
+    <t xml:space="preserve">1647                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3453463456  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">45646465    </t>
+  </si>
+  <si>
     <t xml:space="preserve">C4   </t>
   </si>
   <si>
     <t>Mike</t>
   </si>
   <si>
-    <t>My</t>
-  </si>
-  <si>
     <t>NewYork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6421                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35345355    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34534535    </t>
   </si>
 </sst>
 </file>
@@ -111,15 +132,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -127,12 +154,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,180 +464,191 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1234</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2">
+        <v>123456789</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2">
-        <v>1234</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>123456789</v>
-      </c>
-      <c r="K2">
-        <v>123456789</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3">
-        <v>2222</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3">
-        <v>223344556</v>
-      </c>
-      <c r="K3">
-        <v>223344556</v>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>1647</v>
-      </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>3453463456</v>
-      </c>
-      <c r="K4">
-        <v>45646465</v>
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>6421</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>35345355</v>
-      </c>
-      <c r="K5">
-        <v>34534535</v>
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
